--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,51 +713,111 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>rTrn0h4a</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AcgUMf0E</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+          <t>AsIP75lK</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dionisi f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+          <t>6D3e2qCs</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">santoro a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>tYVGfTo2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -765,25 +825,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">bonacina k 
+          <t xml:space="preserve">sozza s 
   ita </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Qu12kvXf</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>YgLhKnOo</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -791,25 +851,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ghersini d 
+          <t xml:space="preserve">orsato d 
   ita </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>lQEaJ9QD</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -817,25 +877,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">caputi m 
+          <t xml:space="preserve">massa d 
   ita </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tYVGfTo2</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>xjigzK81</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -843,25 +903,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">la penna f 
+          <t xml:space="preserve">santoro a 
   ita </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IZezRssA</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -869,25 +929,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">mariani m 
+          <t xml:space="preserve">manganiello g 
   ita </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>Gfur2NmR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -895,25 +955,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">collu g 
+          <t xml:space="preserve">caputi m 
   ita </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MVSS7qFe</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>YTZ7S7pk</t>
+          <t>619UPLrb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -921,51 +981,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">bonacina k 
   ita </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>8dDPzPa7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>dnnqk0iD</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pairetto l 
-  ita </t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>vD8aDRIm</t>
-        </is>
-      </c>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -973,25 +1024,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">manganiello g 
+          <t xml:space="preserve">ghersini d 
   ita </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -999,25 +1050,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">manganiello g 
+          <t xml:space="preserve">caputi m 
   ita </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>tYVGfTo2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>bs5ow5pA</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1025,51 +1076,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GOfxrOoF</t>
+          <t>IZezRssA</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>02s0k9od</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A72TGDlt</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>Ob5Zdayq</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1077,42 +1119,51 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">pairetto l 
+          <t xml:space="preserve">mariani m 
   ita </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>dnLs0wVo</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>vD8aDRIm</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>n3jv1PNN</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>MVSS7qFe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1120,25 +1171,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">la penna f 
+          <t xml:space="preserve">sozza s 
   ita </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IB8Kk2vH</t>
+          <t>dnLs0wVo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>YgLhKnOo</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>bepKi4a3</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1146,25 +1197,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">bonacina k 
+          <t xml:space="preserve">pairetto l 
   ita </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A72TGDlt</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1172,25 +1223,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">collu g 
+          <t xml:space="preserve">manganiello g 
   ita </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>bmzifXwb</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>YTZ7S7pk</t>
+          <t>Gfur2NmR</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1198,62 +1249,68 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">tremolada p 
+          <t xml:space="preserve">manganiello g 
   ita </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AcgUMf0E</t>
+          <t>Gfur2NmR</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>GOfxrOoF</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>42SH31wI</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sozza s 
-  ita </t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EZS2ir7i</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>YgLhKnOo</t>
-        </is>
-      </c>
+          <t>MVSS7qFe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>fNwTkrUF</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1261,25 +1318,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">colombo a 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2kfSDavF</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>8KIdPmPc</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1288,10 +1345,644 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
+          <t>zFLwLRZS</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>n3jv1PNN</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>IB8Kk2vH</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>A72TGDlt</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AcgUMf0E</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EZS2ir7i</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>CEv2hvmq</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SIJgAihN</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>IZezRssA</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>rTrn0h4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>IB8Kk2vH</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ghersini d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Qu12kvXf</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>A1CicVEU</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>hCxNBHy3</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>KvdW7ZzS</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>n3jv1PNN</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AcgUMf0E</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>GOfxrOoF</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>Eql9v7B6</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>A72TGDlt</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,96 +713,72 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di marco d 
-  ita </t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>rTrn0h4a</t>
+          <t>8dDPzPa7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dnnqk0iD</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tremolada p 
-  ita </t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>n10g3KfJ</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AcgUMf0E</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dionisi f 
-  ita </t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">santoro a 
-  ita </t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>tYVGfTo2</t>
@@ -810,77 +786,58 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>bBhpZV2s</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>bs5ow5pA</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sozza s 
-  ita </t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>IZezRssA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>02s0k9od</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">orsato d 
-  ita </t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>tjY4uUem</t>
-        </is>
-      </c>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>Ob5Zdayq</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">massa d 
-  ita </t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>MLVBCoYg</t>
@@ -888,25 +845,20 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>xjigzK81</t>
+          <t>dnLs0wVo</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">santoro a 
-  ita </t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>MVSS7qFe</t>
@@ -914,14 +866,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>bBhpZV2s</t>
+          <t>YTZ7S7pk</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -929,25 +881,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">manganiello g 
+          <t xml:space="preserve">sozza s 
   ita </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>zFLwLRZS</t>
+          <t>dnLs0wVo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>YgLhKnOo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>bepKi4a3</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -955,25 +907,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">caputi m 
+          <t xml:space="preserve">pairetto l 
   ita </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -981,42 +933,51 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">bonacina k 
+          <t xml:space="preserve">manganiello g 
   ita </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Qu12kvXf</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>Gfur2NmR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>dnnqk0iD</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>Aeu0r0Mk</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1024,51 +985,42 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ghersini d 
+          <t xml:space="preserve">rapuano a 
   ita </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>lQEaJ9QD</t>
+          <t>GOfxrOoF</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>42SH31wI</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">caputi m 
-  ita </t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tYVGfTo2</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>vD8aDRIm</t>
-        </is>
-      </c>
+          <t>MVSS7qFe</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>fNwTkrUF</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1082,19 +1034,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>A72TGDlt</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>AB3WB3pA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>IZezRssA</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>02s0k9od</t>
+          <t>8KIdPmPc</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1103,7 +1055,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1111,7 +1063,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>8KfYbJz0</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1119,51 +1071,42 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">mariani m 
+          <t xml:space="preserve">pairetto l 
   ita </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>dnLs0wVo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>EL1P0u6m</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collu g 
-  ita </t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MVSS7qFe</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>YTZ7S7pk</t>
-        </is>
-      </c>
+          <t>n3jv1PNN</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>M5TEBdK5</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1171,25 +1114,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>IB8Kk2vH</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>joLV7EJU</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1197,25 +1140,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">pairetto l 
+          <t xml:space="preserve">bonacina k 
   ita </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>8dDPzPa7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>WvwvCQVo</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1223,25 +1166,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">manganiello g 
+          <t xml:space="preserve">collu g 
   ita </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>bmzifXwb</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>YTZ7S7pk</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>tYhtcc5C</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1249,68 +1192,62 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">manganiello g 
+          <t xml:space="preserve">tremolada p 
   ita </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>YgLhKnOo</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rapuano a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>GOfxrOoF</t>
-        </is>
-      </c>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
+          <t>SORbFvLt</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MVSS7qFe</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>EZS2ir7i</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>lvG7DIkg</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1318,25 +1255,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">la penna f 
+          <t xml:space="preserve">colombo a 
   ita </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A72TGDlt</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>2kfSDavF</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
+          <t>IXMN9zkI</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1345,7 +1282,7 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>zFLwLRZS</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1353,7 +1290,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>4CX22Dbk</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1361,626 +1298,18 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">pairetto l 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>SIJgAihN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EL1P0u6m</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>n3jv1PNN</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>M5TEBdK5</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>IB8Kk2vH</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>joLV7EJU</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bonacina k 
-  ita </t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>A72TGDlt</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>8dDPzPa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>WvwvCQVo</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collu g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>bmzifXwb</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>YTZ7S7pk</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>tYhtcc5C</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tremolada p 
-  ita </t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>YgLhKnOo</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AcgUMf0E</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>x0nkeyzP</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>SORbFvLt</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sozza s 
-  ita </t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>EZS2ir7i</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>YgLhKnOo</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>lvG7DIkg</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">colombo a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2kfSDavF</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>IXMN9zkI</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>4CX22Dbk</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SIJgAihN</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
           <t>IZezRssA</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>CjGqFjre</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di marco d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>bmzifXwb</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>rTrn0h4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>0IkylEqd</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bonacina k 
-  ita </t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>dnLs0wVo</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>8dDPzPa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>CEhO9e6F</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>CxyB0iT1</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pairetto l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>IB8Kk2vH</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>vD8aDRIm</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>CSXdOfL8</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ghersini d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>vD8aDRIm</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>ptW4MYkL</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Qu12kvXf</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>4QCyHCDr</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doveri d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>O6SinSSs</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>A1CicVEU</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>hCxNBHy3</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>YgLhKnOo</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>KvdW7ZzS</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">manganiello g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Gfur2NmR</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>Y54hDUC7</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tremolada p 
-  ita </t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>n3jv1PNN</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AcgUMf0E</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>v3ivyY4E</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">caputi m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>vD8aDRIm</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>W0WITkcl</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rapuano a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>YgLhKnOo</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>GOfxrOoF</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>YPSZP7dD</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pairetto l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>vD8aDRIm</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>EL5MmBlK</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collu g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>YTZ7S7pk</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>tWk1tTtf</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sozza s 
-  ita </t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>lb1XFX3n</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>Eql9v7B6</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">colombo a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>A72TGDlt</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2kfSDavF</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,7 +539,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">caputi m 
+          <t xml:space="preserve">cosso f 
   ita </t>
         </is>
       </c>
@@ -550,7 +550,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t>bmzifXwb</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">doveri d 
+          <t xml:space="preserve">scatena g 
   ita </t>
         </is>
       </c>
@@ -576,7 +576,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>A1CicVEU</t>
+          <t>WE57Jh0D</t>
         </is>
       </c>
     </row>
@@ -713,120 +713,158 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Qu12kvXf</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dnnqk0iD</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AcgUMf0E</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dionisi f 
+  ita </t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>lQEaJ9QD</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>tYVGfTo2</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>Gfur2NmR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IZezRssA</t>
+          <t>YgLhKnOo</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>02s0k9od</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orsato d 
+  ita </t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -931,12 +969,7 @@
       <c r="B22" t="n">
         <v>1</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">manganiello g 
-  ita </t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>vD8aDRIm</t>
@@ -957,12 +990,7 @@
       <c r="B23" t="n">
         <v>1</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">manganiello g 
-  ita </t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>EJLKYOzb</t>
@@ -983,12 +1011,7 @@
       <c r="B24" t="n">
         <v>1</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rapuano a 
-  ita </t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>n10g3KfJ</t>
@@ -1026,12 +1049,7 @@
       <c r="B26" t="n">
         <v>1</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>A72TGDlt</t>
@@ -1140,7 +1158,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">bonacina k 
+          <t xml:space="preserve">prontera a 
   ita </t>
         </is>
       </c>
@@ -1172,7 +1190,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>bmzifXwb</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1192,7 +1210,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">tremolada p 
+          <t xml:space="preserve">prontera a 
   ita </t>
         </is>
       </c>
@@ -1203,7 +1221,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AcgUMf0E</t>
+          <t>8dDPzPa7</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1300,7 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1310,6 +1328,170 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>IZezRssA</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>rTrn0h4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>IB8Kk2vH</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>A1CicVEU</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,59 +453,49 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zufferli l 
-  ita </t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">orsato d 
-  ita </t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>tYVGfTo2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>EZS2ir7i</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +503,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">maresca f 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A72TGDlt</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4IdjsvY2</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +529,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">cosso f 
+          <t xml:space="preserve">tremolada p 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>bmzifXwb</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,7 +555,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">scatena g 
+          <t xml:space="preserve">perri m 
   ita </t>
         </is>
       </c>
@@ -576,14 +566,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WE57Jh0D</t>
+          <t>hrkecaMB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +581,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">dionisi f 
+          <t xml:space="preserve">feliciani e 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +607,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">massa d 
+          <t xml:space="preserve">tremolada p 
   ita </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>zFLwLRZS</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>xjigzK81</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,25 +633,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">orsato d 
   ita </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Qu12kvXf</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -669,25 +659,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">orsato d 
+          <t xml:space="preserve">fabbri m 
   ita </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MVSS7qFe</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -695,25 +685,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">manganiello g 
+          <t xml:space="preserve">caputi m 
   ita </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>tYVGfTo2</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -721,25 +711,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">collu g 
   ita </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>rTrn0h4a</t>
+          <t>EZS2ir7i</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -747,25 +737,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">tremolada p 
+          <t xml:space="preserve">caputi m 
   ita </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AcgUMf0E</t>
+          <t>619UPLrb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -773,7 +763,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">dionisi f 
+          <t xml:space="preserve">maresca f 
   ita </t>
         </is>
       </c>
@@ -784,14 +774,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -799,25 +789,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">orsato d 
   ita </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -825,25 +815,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">fabbri m 
   ita </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -851,67 +841,77 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">orsato d 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>xjigzK81</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maresca f 
+  ita </t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MVSS7qFe</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>YTZ7S7pk</t>
+          <t>619UPLrb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -919,25 +919,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">fabbri m 
   ita </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -945,143 +945,181 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">pairetto l 
+          <t xml:space="preserve">marchetti m 
   ita </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>23vSAc12</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>tYVGfTo2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>xjigzK81</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>EZS2ir7i</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>4CX22Dbk</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>bmzifXwb</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GOfxrOoF</t>
+          <t>tvh4IkLf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
+          <t>CjGqFjre</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MVSS7qFe</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>0IkylEqd</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A72TGDlt</t>
+          <t>lb1XFX3n</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>8dDPzPa7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
+          <t>CEhO9e6F</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>zFLwLRZS</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>CxyB0iT1</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1089,42 +1127,51 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">pairetto l 
+          <t xml:space="preserve">aureliano g 
   ita </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>GfucctAF</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>Wn0poKgt</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>CSXdOfL8</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>n3jv1PNN</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>ptW4MYkL</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1132,25 +1179,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">la penna f 
+          <t xml:space="preserve">prontera a 
   ita </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IB8Kk2vH</t>
+          <t>nsYMfLJM</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>lSb6U6l0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>4QCyHCDr</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1158,25 +1205,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">prontera a 
+          <t xml:space="preserve">abisso r 
   ita </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A72TGDlt</t>
+          <t>GfucctAF</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>2kfSDavF</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>hCxNBHy3</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1190,19 +1237,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>nsYMfLJM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>YTZ7S7pk</t>
+          <t>tvh4IkLf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>KvdW7ZzS</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1210,36 +1257,51 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">prontera a 
+          <t xml:space="preserve">bonacina k 
   ita </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>YgLhKnOo</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>8dDPzPa7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>v3ivyY4E</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1247,25 +1309,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">perri m 
   ita </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EZS2ir7i</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>YTZ7S7pk</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>W0WITkcl</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1273,42 +1335,51 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">colombo a 
+          <t xml:space="preserve">manganiello g 
   ita </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>OjWmexQb</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2kfSDavF</t>
+          <t>O6SinSSs</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>YPSZP7dD</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>EL5MmBlK</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1316,25 +1387,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">la penna f 
+          <t xml:space="preserve">perri m 
   ita </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SIJgAihN</t>
+          <t>dnLs0wVo</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IZezRssA</t>
+          <t>YTZ7S7pk</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>tWk1tTtf</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1342,25 +1413,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">aureliano g 
   ita </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>Gfur2NmR</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>rTrn0h4a</t>
+          <t>Wn0poKgt</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>0IkylEqd</t>
+          <t>Eql9v7B6</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1368,42 +1439,51 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">prontera a 
+          <t xml:space="preserve">abisso r 
   ita </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>OjWmexQb</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>2kfSDavF</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
+          <t>zVpmZBZQ</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CxyB0iT1</t>
+          <t>SSPRRTR0</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1411,25 +1491,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">pairetto l 
+          <t xml:space="preserve">manganiello g 
   ita </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IB8Kk2vH</t>
+          <t>Yika9O16</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>O6SinSSs</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>CSXdOfL8</t>
+          <t>p4dhrkCs</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1437,42 +1517,51 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">arena a 
   ita </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>nZ24J27c</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>hrkecaMB</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>ptW4MYkL</t>
+          <t>v3JgRFm3</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>bPHSQi9q</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>4QCyHCDr</t>
+          <t>dtLQNtsB</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1480,18 +1569,226 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">doveri d 
+          <t xml:space="preserve">fourneau f 
   ita </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>O6SinSSs</t>
+          <t>bmzifXwb</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>A1CicVEU</t>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Ofy73Ced</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>CGH1PgIF</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>21OYHBAk</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>v5l07LdU</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>fHO9ROsn</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>jqIIP2Cb</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zufferli l 
+          <t xml:space="preserve">maresca f 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">orsato d 
+          <t xml:space="preserve">tremolada p 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">massa d 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A72TGDlt</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4IdjsvY2</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">cosso f 
+          <t xml:space="preserve">feliciani e 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>bmzifXwb</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">scatena g 
+          <t xml:space="preserve">tremolada p 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WE57Jh0D</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">dionisi f 
+          <t xml:space="preserve">massa d 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">massa d 
+          <t xml:space="preserve">fabbri m 
   ita </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>zFLwLRZS</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>xjigzK81</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">caputi m 
   ita </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Qu12kvXf</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -669,25 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">orsato d 
+          <t xml:space="preserve">marcenaro m 
   ita </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MVSS7qFe</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -695,25 +695,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">manganiello g 
+          <t xml:space="preserve">marcenaro m 
   ita </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>tYVGfTo2</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -721,25 +721,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">maresca f 
   ita </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>rTrn0h4a</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -747,25 +747,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">tremolada p 
+          <t xml:space="preserve">massa d 
   ita </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AcgUMf0E</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -773,25 +773,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">dionisi f 
+          <t xml:space="preserve">fabbri m 
   ita </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -799,25 +799,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>xjigzK81</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -825,25 +825,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">maresca f 
   ita </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -851,67 +851,77 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">orsato d 
+          <t xml:space="preserve">ayroldi g 
   ita </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>619UPLrb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MVSS7qFe</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>YTZ7S7pk</t>
+          <t>23vSAc12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -919,25 +929,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>xjigzK81</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -945,143 +955,181 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">pairetto l 
+          <t xml:space="preserve">marcenaro m 
   ita </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>4CX22Dbk</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>bmzifXwb</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>tvh4IkLf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>CjGqFjre</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>bmzifXwb</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>8dDPzPa7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>0IkylEqd</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>lb1XFX3n</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GOfxrOoF</t>
+          <t>8dDPzPa7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
+          <t>CEhO9e6F</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MVSS7qFe</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>CxyB0iT1</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A72TGDlt</t>
+          <t>GfucctAF</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>Wn0poKgt</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
+          <t>CSXdOfL8</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>zFLwLRZS</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>ptW4MYkL</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1089,42 +1137,51 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">pairetto l 
+          <t xml:space="preserve">prontera a 
   ita </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>nsYMfLJM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>lSb6U6l0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>4QCyHCDr</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>n3jv1PNN</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>hCxNBHy3</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1132,25 +1189,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">la penna f 
+          <t xml:space="preserve">collu g 
   ita </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IB8Kk2vH</t>
+          <t>nsYMfLJM</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>tvh4IkLf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>KvdW7ZzS</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1158,25 +1215,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">prontera a 
+          <t xml:space="preserve">bonacina k 
   ita </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A72TGDlt</t>
+          <t>Gfur2NmR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>YgLhKnOo</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>Y54hDUC7</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1184,25 +1241,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">collu g 
+          <t xml:space="preserve">piccinini m 
   ita </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>nZ24J27c</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>YTZ7S7pk</t>
+          <t>bPHSQi9q</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>v3ivyY4E</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1210,36 +1267,51 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">prontera a 
+          <t xml:space="preserve">perri m 
   ita </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>YTZ7S7pk</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>YPSZP7dD</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1247,25 +1319,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">aureliano g 
   ita </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EZS2ir7i</t>
+          <t>Yika9O16</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>Wn0poKgt</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>EL5MmBlK</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1273,42 +1345,51 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">colombo a 
+          <t xml:space="preserve">perri m 
   ita </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>dnLs0wVo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2kfSDavF</t>
+          <t>YTZ7S7pk</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>tWk1tTtf</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>Eql9v7B6</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1316,25 +1397,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">la penna f 
+          <t xml:space="preserve">abisso r 
   ita </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SIJgAihN</t>
+          <t>OjWmexQb</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IZezRssA</t>
+          <t>2kfSDavF</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>zVpmZBZQ</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1342,25 +1423,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">piccinini m 
   ita </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>rTrn0h4a</t>
+          <t>bPHSQi9q</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>0IkylEqd</t>
+          <t>SSPRRTR0</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1368,42 +1449,51 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">prontera a 
+          <t xml:space="preserve">manganiello g 
   ita </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>Yika9O16</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>O6SinSSs</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
+          <t>p4dhrkCs</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CxyB0iT1</t>
+          <t>v3JgRFm3</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1411,25 +1501,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">pairetto l 
+          <t xml:space="preserve">collu g 
   ita </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IB8Kk2vH</t>
+          <t>dnLs0wVo</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>tvh4IkLf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>CSXdOfL8</t>
+          <t>dtLQNtsB</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1437,42 +1527,51 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">di marco d 
+          <t xml:space="preserve">fourneau f 
   ita </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>bmzifXwb</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>8dDPzPa7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>ptW4MYkL</t>
+          <t>Ofy73Ced</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena a 
+  ita </t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>bPHSQi9q</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>hrkecaMB</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>4QCyHCDr</t>
+          <t>CGH1PgIF</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1480,18 +1579,174 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">doveri d 
+          <t xml:space="preserve">bonacina k 
   ita </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>O6SinSSs</t>
+          <t>nsYMfLJM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>A1CicVEU</t>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>21OYHBAk</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>v5l07LdU</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>fHO9ROsn</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collu g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>tvh4IkLf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>jqIIP2Cb</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bonacina k 
+  ita </t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,786 +970,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>4CX22Dbk</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collu g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>bmzifXwb</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>tvh4IkLf</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>CjGqFjre</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fourneau f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>bmzifXwb</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>8dDPzPa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>0IkylEqd</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fourneau f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>lb1XFX3n</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>8dDPzPa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>CEhO9e6F</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prontera a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Yika9O16</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>lSb6U6l0</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CxyB0iT1</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aureliano g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>GfucctAF</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Wn0poKgt</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>CSXdOfL8</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">arena a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>dnLs0wVo</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>hrkecaMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>ptW4MYkL</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prontera a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>nsYMfLJM</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>lSb6U6l0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>4QCyHCDr</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">abisso r 
-  ita </t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>GfucctAF</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2kfSDavF</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>hCxNBHy3</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collu g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>nsYMfLJM</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>tvh4IkLf</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>KvdW7ZzS</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bonacina k 
-  ita </t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Gfur2NmR</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>YgLhKnOo</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Y54hDUC7</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">piccinini m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>nZ24J27c</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>bPHSQi9q</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>v3ivyY4E</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">perri m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>vD8aDRIm</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>YTZ7S7pk</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>W0WITkcl</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">manganiello g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>OjWmexQb</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>O6SinSSs</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>YPSZP7dD</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aureliano g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Yika9O16</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Wn0poKgt</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>EL5MmBlK</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">perri m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>dnLs0wVo</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>YTZ7S7pk</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>tWk1tTtf</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aureliano g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Gfur2NmR</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Wn0poKgt</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Eql9v7B6</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">abisso r 
-  ita </t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>OjWmexQb</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2kfSDavF</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>zVpmZBZQ</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">piccinini m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>vD8aDRIm</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>bPHSQi9q</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>SSPRRTR0</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">manganiello g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Yika9O16</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>O6SinSSs</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>p4dhrkCs</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">arena a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>nZ24J27c</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>hrkecaMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>v3JgRFm3</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collu g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>dnLs0wVo</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>tvh4IkLf</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>dtLQNtsB</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fourneau f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>bmzifXwb</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>8dDPzPa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>Ofy73Ced</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">arena a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>GfucctAF</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>hrkecaMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>CGH1PgIF</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bonacina k 
-  ita </t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>nsYMfLJM</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>YgLhKnOo</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>21OYHBAk</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aureliano g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>bmzifXwb</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Wn0poKgt</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>v5l07LdU</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prontera a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>nsYMfLJM</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>lSb6U6l0</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>fHO9ROsn</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collu g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>dnLs0wVo</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>tvh4IkLf</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>jqIIP2Cb</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fourneau f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Gfur2NmR</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>8dDPzPa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>GUXb5YQq</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bonacina k 
-  ita </t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>lb1XFX3n</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>YgLhKnOo</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>WIX2NXnS</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prontera a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>GfucctAF</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>lSb6U6l0</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -461,16 +456,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">maresca f 
-  ita </t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>AB3WB3pA</t>
         </is>
@@ -487,16 +476,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tremolada p 
-  ita </t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>tjY4uUem</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>n10g3KfJ</t>
         </is>
@@ -513,16 +496,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">massa d 
-  ita </t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>EJLKYOzb</t>
         </is>
@@ -539,434 +516,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">feliciani e 
-  ita </t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
           <t>j32a3mqs</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>M7MVoOR0</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tremolada p 
-  ita </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>dbt7KrYP</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">massa d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>UilLdutJ</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fabbri m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MLVBCoYg</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>2uc40Ntf</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">caputi m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>0hYMmpcl</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marcenaro m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>MLVBCoYg</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>fZZxp2dD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marcenaro m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>EaryFQkA</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">maresca f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>S8Ygn9ME</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>WdSjHeFt</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">massa d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>ELeQ0zVa</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fabbri m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>tjY4uUem</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>d4DGBiqI</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>KtGrCa5d</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>xjigzK81</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0xK7DDE5</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">maresca f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>S8Ygn9ME</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>SjzlgqTj</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>619UPLrb</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fabbri m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marchetti m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>xjigzK81</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marcenaro m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>tjY4uUem</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,80 +453,386 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>lQEaJ9QD</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>tjY4uUem</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maresca f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marcenaro m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -462,19 +462,19 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lQEaJ9QD</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,103 +483,123 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>xjigzK81</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -587,25 +607,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">maresca f 
+          <t xml:space="preserve">sacchi j  l 
   ita </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -613,25 +633,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">massa d 
+          <t xml:space="preserve">sacchi j  l 
   ita </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -639,25 +659,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">fabbri m 
+          <t xml:space="preserve">mariani m 
   ita </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -665,25 +685,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">la penna f 
+          <t xml:space="preserve">marchetti m 
   ita </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>xjigzK81</t>
+          <t>23vSAc12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -691,25 +711,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>xjigzK81</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -717,120 +737,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
+          <t xml:space="preserve">marcenaro m 
   ita </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fabbri m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marchetti m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>xjigzK81</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marcenaro m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
         <is>
           <t>YXIDwoe5</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,49 +453,59 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -503,25 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
+          <t xml:space="preserve">zufferli l 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -529,7 +539,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
+          <t xml:space="preserve">di bello m 
   ita </t>
         </is>
       </c>
@@ -540,14 +550,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -555,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fabbri m 
+          <t xml:space="preserve">sacchi j  l 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -581,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">la penna f 
+          <t xml:space="preserve">sacchi j  l 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>xjigzK81</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -607,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
+          <t xml:space="preserve">mariani m 
   ita </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -633,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
+          <t xml:space="preserve">giua a 
   ita </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -659,25 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">mariani m 
+          <t xml:space="preserve">zufferli l 
   ita </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -685,68 +695,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">marchetti m 
+          <t xml:space="preserve">di bello m 
   ita </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>xjigzK81</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marcenaro m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
         <is>
           <t>YXIDwoe5</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
-  ita </t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
-  ita </t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">zufferli l 
-  ita </t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +536,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
-  ita </t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +556,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
-  ita </t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +576,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mariani m 
-  ita </t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,68 +596,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">giua a 
-  ita </t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zufferli l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
         <is>
           <t>YXIDwoe5</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,90 +516,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>619UPLrb</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
         <is>
           <t>YXIDwoe5</t>
         </is>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>n7VN5MCd</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t xml:space="preserve">marinelli l 
+  ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>v1I9TP43</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t xml:space="preserve">guida m 
+  ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>bBhpZV2s</t>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>SQjcKLRk</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t xml:space="preserve">marcenaro m 
+  ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,12 +539,174 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t xml:space="preserve">guida m 
+  ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>YXIDwoe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -710,6 +710,266 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marinelli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marcenaro m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marinelli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prontera a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>n7VN5MCd</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">marinelli l 
-  ita </t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
+          <t>xjigzK81</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>v1I9TP43</t>
+          <t>zFWqD4KM</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">guida m 
-  ita </t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>xjigzK81</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SQjcKLRk</t>
+          <t>4WHcOkpL</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">marcenaro m 
-  ita </t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>6cNF7rrp</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">guida m 
-  ita </t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>xjigzK81</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>Esk5Iad2</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +536,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">colombo a 
-  ita </t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>WIJkQBF8</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +556,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fabbri m 
-  ita </t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MLVBCoYg</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>rgFQPs4S</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,356 +576,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">tremolada p 
-  ita </t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Esk5Iad2</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marchetti m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>619UPLrb</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WIJkQBF8</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prontera a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rgFQPs4S</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>S8Ygn9ME</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>OW6PtuKn</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2ucWYubt</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marinelli l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>KtGrCa5d</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>44gmVcc5</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marcenaro m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>S66wtFBN</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Yqo4RFdU</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tremolada p 
-  ita </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>O8QDoJsn</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tremolada p 
-  ita </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>KtGrCa5d</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>A50vXJSh</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">massa d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>619UPLrb</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>pOEMqcCb</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marinelli l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>619UPLrb</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>WvDUsysB</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prontera a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>xIieTySH</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">massa d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>OAeKROjD</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prontera a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>2ucWYubt</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t xml:space="preserve">di bello m 
+  ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>xjigzK81</t>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>44gmVcc5</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
+          <t xml:space="preserve">colombo a 
+  ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t xml:space="preserve">giua a 
+  ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t xml:space="preserve">la penna f 
+  ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lQEaJ9QD</t>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,19 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t xml:space="preserve">abisso r 
+  ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -556,19 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -576,12 +617,356 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>OW6PtuKn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di marco d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2ucWYubt</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
+          <t>xjigzK81</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>44gmVcc5</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">colombo a 
-  ita </t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>KtGrCa5d</t>
+          <t>23vSAc12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>S66wtFBN</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">giua a 
-  ita </t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>xjigzK81</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Yqo4RFdU</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>O8QDoJsn</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +536,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">abisso r 
-  ita </t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>A50vXJSh</t>
+          <t>WvDUsysB</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +556,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">zufferli l 
-  ita </t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pOEMqcCb</t>
+          <t>xIieTySH</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +576,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">piccinini m 
-  ita </t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>tjY4uUem</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WvDUsysB</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,330 +596,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">abisso r 
-  ita </t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>xIieTySH</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di marco d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OAeKROjD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">piccinini m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>tjY4uUem</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CCDxBZAc</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">colombo a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>KtGrCa5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pIgDNCf3</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pairetto l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>KIQjmWIj</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Whh3dzd4</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sacchi j  l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>619UPLrb</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>WxCQa92d</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zufferli l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OC8I1VXq</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di marco d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zufferli l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sacchi j  l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>619UPLrb</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pairetto l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>MLVBCoYg</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,27 +453,28 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>xjigzK81</t>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +482,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>j32a3mqs</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +508,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t xml:space="preserve">mariani m 
+  ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +534,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t xml:space="preserve">doveri d 
+  ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lQEaJ9QD</t>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,19 +560,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>619UPLrb</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -556,19 +586,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t xml:space="preserve">marcenaro m 
+  ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -576,12 +612,382 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marinelli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marcenaro m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>S8Ygn9ME</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EB8yv2aJ</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marchetti m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marinelli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,28 +448,27 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OAeKROjD</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>tjY4uUem</t>
+          <t>bPHSQi9q</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -482,25 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">guida m 
-  ita </t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -508,25 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">mariani m 
-  ita </t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4IdjsvY2</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
+          <t>23vSAc12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -534,25 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">doveri d 
-  ita </t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -560,25 +536,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
-  ita </t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>619UPLrb</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -586,25 +556,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">marcenaro m 
-  ita </t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>S8Ygn9ME</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -612,25 +576,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">marchetti m 
-  ita </t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4IdjsvY2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -638,25 +596,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">marinelli l 
-  ita </t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -664,330 +616,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">marcenaro m 
-  ita </t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>S8Ygn9ME</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">massa d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>tjY4uUem</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sozza s 
-  ita </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>KtGrCa5d</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>z3jsi9f5</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">piccinini m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>tjY4uUem</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8SWavWAa</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marchetti m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WUqjkmPH</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">guida m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4IdjsvY2</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>EB8yv2aJ</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marchetti m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ttV7xAuC</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marinelli l 
-  ita </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>x8OGzlAO</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sozza s 
-  ita </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dzYLoEIP</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">guida m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SW3Qfiet</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sozza s 
-  ita </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>619UPLrb</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>lnhZhVPh</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feliciani e 
-  ita </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SIOithtm</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mariani m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>619UPLrb</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
+          <t>lb1XFX3n</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>bPHSQi9q</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,19 +536,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>lb1XFX3n</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -556,72 +556,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4IdjsvY2</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>S8Ygn9ME</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>lb1XFX3n</t>
+          <t>YgLhKnOo</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,120 +453,262 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>z3jsi9f5</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>8SWavWAa</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>4IdjsvY2</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>WUqjkmPH</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>EB8yv2aJ</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>ttV7xAuC</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lb1XFX3n</t>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>KtGrCa5d</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>YgLhKnOo</t>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -462,19 +462,19 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,19 +483,19 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -504,19 +504,19 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>619UPLrb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -525,19 +525,19 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>bBhpZV2s</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -546,28 +546,33 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -579,76 +584,96 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>MBrKQFV7</t>
@@ -656,14 +681,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -671,25 +696,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">fourneau f 
+          <t xml:space="preserve">aureliano g 
   ita </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>619UPLrb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -697,18 +722,70 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
+          <t xml:space="preserve">chiffi d 
   ita </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>tSiEeKvS</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,112 +453,137 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -566,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fourneau f 
+          <t xml:space="preserve">pairetto l 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -592,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">rapuano a 
+          <t xml:space="preserve">chiffi d 
   ita </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SznSCTAl</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -618,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">mariani m 
+          <t xml:space="preserve">marcenaro m 
   ita </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2g2mKBIE</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -644,25 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">marcenaro m 
   ita </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -670,25 +695,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">feliciani e 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -696,7 +721,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">aureliano g 
+          <t xml:space="preserve">marinelli l 
   ita </t>
         </is>
       </c>
@@ -707,14 +732,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -722,25 +747,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">chiffi d 
+          <t xml:space="preserve">feliciani e 
   ita </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -748,25 +773,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">sozza s 
+          <t xml:space="preserve">mariani m 
   ita </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>lQEaJ9QD</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -774,18 +799,252 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">sacchi j  l 
+          <t xml:space="preserve">pairetto l 
   ita </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OMVUWl2K</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marinelli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>4IdjsvY2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>j32a3mqs</t>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,12 +459,7 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>23vSAc12</t>
@@ -485,12 +480,7 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>EJLKYOzb</t>
@@ -511,12 +501,7 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mariani m 
-  ita </t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>619UPLrb</t>
@@ -537,12 +522,7 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>bBhpZV2s</t>
@@ -563,12 +543,7 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feliciani e 
-  ita </t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>S8Ygn9ME</t>
@@ -589,12 +564,7 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pairetto l 
-  ita </t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>ncu4OLs5</t>
@@ -615,12 +585,7 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chiffi d 
-  ita </t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>OW6PtuKn</t>
@@ -641,12 +606,7 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marcenaro m 
-  ita </t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>bBhpZV2s</t>
@@ -667,12 +627,7 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marcenaro m 
-  ita </t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>CEv2hvmq</t>
@@ -693,12 +648,7 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>OW6PtuKn</t>
@@ -1045,6 +995,136 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>YXIDwoe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marcenaro m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">di bello m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,6 +1128,58 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marcenaro m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bBhpZV2s</t>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>OMVUWl2K</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,19 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t xml:space="preserve">dionisi f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>McP0d8Q7</t>
+          <t>jeAhPc0B</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -556,12 +591,642 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>OW6PtuKn</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dionisi f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">abisso r 
+  ita </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dionisi f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sacchi j  l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aureliano g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,180 +453,730 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>I5fXHFho</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bLD0NyVN</t>
+          <t>4CLi9Djd</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MLVBCoYg</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>lQEaJ9QD</t>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UuMqRJVb</t>
+          <t>WIDwXGr3</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OMVUWl2K</t>
+          <t>IFm4IHT9</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jeAhPc0B</t>
+          <t>0b5fTYsS</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OjcQLOgJ</t>
+          <t>Y96v2dqT</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>xY3xTu1n</t>
+          <t>rcXrBZLq</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jwaINpP6</t>
+          <t>EssDGebM</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>4IdjsvY2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>S8Ygn9ME</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fB59P6ff</t>
+          <t>Sp7nVfDF</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>KtGrCa5d</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">guida m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rapuano a 
+  ita </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>bR8Aj2ug</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OYgzob9U</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>23vSAc12</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hO2h1JgB</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">la penna f 
+  ita </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>E3zhYKPO</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>S60RnKvI</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ayroldi g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>tjxpzseC</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">manganiello g 
+  ita </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>pbap3uPb</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doveri d 
+  ita </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>hU52hOAt</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feliciani e 
+  ita </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>voUq51fn</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>KtcJltA5</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tremolada p 
+  ita </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,730 +453,260 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Ug79dz7j</t>
+          <t>rJ8JNC5k</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mariani m 
+  ita </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4CLi9Djd</t>
+          <t>pOryx3Qa</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zufferli l 
+  ita </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WIDwXGr3</t>
+          <t>Gpn0zjke</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colombo a 
+  ita </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>23vSAc12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IFm4IHT9</t>
+          <t>CCu9YTJ7</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piccinini m 
+  ita </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lQEaJ9QD</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>bBhpZV2s</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0b5fTYsS</t>
+          <t>b7pTwPem</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CEv2hvmq</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>619UPLrb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Y96v2dqT</t>
+          <t>WvkEqfS8</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fabbri m 
+  ita </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rcXrBZLq</t>
+          <t>v5hMsYdL</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">massa d 
+  ita </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
+          <t>MBrKQFV7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EssDGebM</t>
+          <t>jqCRLjz2</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pairetto l 
+  ita </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>S8Ygn9ME</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>4IdjsvY2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Sp7nVfDF</t>
+          <t>vJXfdXBE</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chiffi d 
+  ita </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>619UPLrb</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>p2kdKwac</t>
+          <t>rXmhxCKr</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fourneau f 
+  ita </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>rJ8JNC5k</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tremolada p 
-  ita </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>KtGrCa5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pOryx3Qa</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">guida m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>bBhpZV2s</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Gpn0zjke</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chiffi d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>CCu9YTJ7</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feliciani e 
-  ita </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>b7pTwPem</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sozza s 
-  ita </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>4IdjsvY2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WvkEqfS8</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sozza s 
-  ita </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>4IdjsvY2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>v5hMsYdL</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rapuano a 
-  ita </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>jqCRLjz2</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>vJXfdXBE</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">piccinini m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>lQEaJ9QD</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>rXmhxCKr</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">manganiello g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>S8Ygn9ME</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>MLVBCoYg</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>bR8Aj2ug</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>S8Ygn9ME</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>OYgzob9U</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>hO2h1JgB</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>MBrKQFV7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>E3zhYKPO</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chiffi d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ncu4OLs5</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>S60RnKvI</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>YXIDwoe5</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>tjxpzseC</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">manganiello g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>MLVBCoYg</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>pbap3uPb</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doveri d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>619UPLrb</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
           <t>tjY4uUem</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>hU52hOAt</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feliciani e 
-  ita </t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>619UPLrb</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>voUq51fn</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">piccinini m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>tSiEeKvS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>KtcJltA5</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tremolada p 
-  ita </t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>KtGrCa5d</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rJ8JNC5k</t>
+          <t>bR8Aj2ug</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mariani m 
+          <t xml:space="preserve">di bello m 
   ita </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pOryx3Qa</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">zufferli l 
+          <t xml:space="preserve">di bello m 
   ita </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>n10g3KfJ</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>lQEaJ9QD</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gpn0zjke</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">colombo a 
+          <t xml:space="preserve">guida m 
   ita </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CCu9YTJ7</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">piccinini m 
+          <t xml:space="preserve">feliciani e 
   ita </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>KAwSWnoE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b7pTwPem</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,13 +565,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">chiffi d 
+          <t xml:space="preserve">la penna f 
   ita </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4IdjsvY2</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -583,7 +583,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WvkEqfS8</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fabbri m 
+          <t xml:space="preserve">abisso r 
   ita </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AB3WB3pA</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v5hMsYdL</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">massa d 
+          <t xml:space="preserve">collu g 
   ita </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jqCRLjz2</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">pairetto l 
+          <t xml:space="preserve">marcenaro m 
   ita </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vJXfdXBE</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -669,25 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">chiffi d 
+          <t xml:space="preserve">ayroldi g 
   ita </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bBhpZV2s</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rXmhxCKr</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -695,18 +695,18 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">fourneau f 
+          <t xml:space="preserve">doveri d 
   ita </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/italy/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,21 +453,16 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lQEaJ9QD</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -479,234 +474,220 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">di bello m 
-  ita </t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">guida m 
-  ita </t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>j32a3mqs</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>tSiEeKvS</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feliciani e 
-  ita </t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>619UPLrb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">la penna f 
-  ita </t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>619UPLrb</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>hU52hOAt</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AB3WB3pA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>voUq51fn</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>KtcJltA5</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WENRFI84</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OW6PtuKn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z7KrCz8T</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">abisso r 
   ita </t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>23vSAc12</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>bBhpZV2s</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>pbap3uPb</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collu g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>OW6PtuKn</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>KtGrCa5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>hU52hOAt</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marcenaro m 
-  ita </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>AB3WB3pA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>4IdjsvY2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>voUq51fn</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ayroldi g 
-  ita </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CEv2hvmq</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MLVBCoYg</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>KtcJltA5</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doveri d 
-  ita </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>EJLKYOzb</t>
         </is>
       </c>
     </row>
